--- a/data/gravel/Panorama Katahdin 2.1 2025.xlsx
+++ b/data/gravel/Panorama Katahdin 2.1 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CBE5A3-0CD1-6242-9E7A-5552B34A530F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560B05FC-9499-284B-A8F8-0FCE6F5029F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
+    <workbookView xWindow="320" yWindow="500" windowWidth="27120" windowHeight="16600" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Panorama Katahdin 2.1 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="99">
   <si>
     <t>brand</t>
   </si>
@@ -59,12 +59,6 @@
     <t>carbon</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>measure range</t>
   </si>
   <si>
@@ -221,14 +215,131 @@
     <t>yes</t>
   </si>
   <si>
-    <t>a10:e33</t>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>BSA 68</t>
+  </si>
+  <si>
+    <t>50/34</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>a10:e34</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -330,6 +441,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura Medium"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -351,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -371,6 +500,15 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,34 +944,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299AF885-3999-4E4F-8F92-5857EF0F7F08}">
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:AH46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.83203125" style="1" customWidth="1"/>
-    <col min="3" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="1"/>
-    <col min="10" max="24" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="5" width="12.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="9" width="16" style="1" customWidth="1"/>
+    <col min="10" max="28" width="12.5" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -841,7 +980,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -849,58 +988,236 @@
         <v>45855</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" s="19" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="O6" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="P6" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q6" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="R6" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="S6" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="T6" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="U6" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="V6" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="W6" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="X6" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y6" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z6" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB6" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC6" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD6" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE6" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF6" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG6" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH6" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" s="1">
+        <v>142</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="M7" s="1">
+        <v>27.2</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R7" s="1">
+        <v>46</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>160</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>160</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>1899</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>3299</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH7" s="22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>36</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>38</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -914,12 +1231,12 @@
       <c r="P10"/>
       <c r="Q10" s="3"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1">
         <v>745</v>
@@ -942,12 +1259,12 @@
       <c r="P11" s="13"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" s="16">
         <v>70</v>
@@ -970,12 +1287,12 @@
       <c r="P12" s="13"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" s="16">
         <v>74</v>
@@ -998,12 +1315,12 @@
       <c r="P13" s="13"/>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" s="16">
         <v>573</v>
@@ -1026,12 +1343,12 @@
       <c r="P14" s="13"/>
       <c r="Q14" s="3"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C15" s="16">
         <v>382</v>
@@ -1054,12 +1371,12 @@
       <c r="P15" s="13"/>
       <c r="Q15" s="3"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" s="16">
         <v>145</v>
@@ -1084,10 +1401,10 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C17" s="16">
         <v>450</v>
@@ -1112,10 +1429,10 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="16">
         <v>546</v>
@@ -1142,10 +1459,10 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" s="16">
         <v>432</v>
@@ -1172,10 +1489,10 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C20" s="16">
         <v>75</v>
@@ -1202,10 +1519,10 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="16">
         <v>55</v>
@@ -1232,10 +1549,10 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C22" s="16">
         <v>1040</v>
@@ -1262,10 +1579,10 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" s="16">
         <v>71</v>
@@ -1292,10 +1609,10 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C24" s="16">
         <v>70</v>
@@ -1322,7 +1639,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -1344,7 +1661,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -1365,7 +1682,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -1386,7 +1703,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -1408,16 +1725,13 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="16">
-        <v>700</v>
-      </c>
-      <c r="D29" s="16">
-        <v>700</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
       <c r="E29" s="16">
-        <v>700</v>
+        <v>1350</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="16"/>
@@ -1435,16 +1749,16 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C30" s="16">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="D30" s="16">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="E30" s="16">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
@@ -1462,23 +1776,18 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C31" s="16">
-        <f>2.25*25.4</f>
-        <v>57.15</v>
+        <v>45</v>
       </c>
       <c r="D31" s="16">
-        <f t="shared" ref="D31:E31" si="0">2.25*25.4</f>
-        <v>57.15</v>
+        <v>45</v>
       </c>
       <c r="E31" s="16">
-        <f t="shared" si="0"/>
-        <v>57.15</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>57</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F31" s="16"/>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
       <c r="J31" s="13"/>
@@ -1494,76 +1803,83 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="1">
-        <f>C34*2.54</f>
-        <v>162.56</v>
-      </c>
-      <c r="D32" s="1">
-        <f t="shared" ref="D32:E33" si="1">D34*2.54</f>
-        <v>170.18</v>
-      </c>
-      <c r="E32" s="1">
-        <f t="shared" si="1"/>
-        <v>177.8</v>
-      </c>
-      <c r="I32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32"/>
-      <c r="P32"/>
+        <v>28</v>
+      </c>
+      <c r="C32" s="16">
+        <f>2.25*25.4</f>
+        <v>57.15</v>
+      </c>
+      <c r="D32" s="16">
+        <f t="shared" ref="D32:E32" si="0">2.25*25.4</f>
+        <v>57.15</v>
+      </c>
+      <c r="E32" s="16">
+        <f t="shared" si="0"/>
+        <v>57.15</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
       <c r="Q32" s="10"/>
       <c r="R32" s="10"/>
       <c r="S32" s="10"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="1">
         <f>C35*2.54</f>
+        <v>162.56</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" ref="D33:E34" si="1">D35*2.54</f>
         <v>170.18</v>
       </c>
-      <c r="D33" s="1">
+      <c r="E33" s="1">
         <f t="shared" si="1"/>
         <v>177.8</v>
       </c>
-      <c r="E33" s="1">
-        <f t="shared" si="1"/>
-        <v>187.96</v>
-      </c>
+      <c r="I33"/>
       <c r="J33"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
       <c r="S33" s="10"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="B34" s="14"/>
-      <c r="C34" s="14">
-        <v>64</v>
-      </c>
-      <c r="D34" s="14">
-        <v>67</v>
-      </c>
-      <c r="E34" s="14">
-        <v>70</v>
-      </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="J34" s="11"/>
+      <c r="C34" s="1">
+        <f>C36*2.54</f>
+        <v>170.18</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="1"/>
+        <v>177.8</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" si="1"/>
+        <v>187.96</v>
+      </c>
+      <c r="J34"/>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
@@ -1575,15 +1891,19 @@
       <c r="S34" s="10"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="C35" s="1">
+      <c r="B35" s="14"/>
+      <c r="C35" s="14">
+        <v>64</v>
+      </c>
+      <c r="D35" s="14">
         <v>67</v>
       </c>
-      <c r="D35" s="1">
+      <c r="E35" s="14">
         <v>70</v>
       </c>
-      <c r="E35" s="1">
-        <v>74</v>
-      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
@@ -1595,21 +1915,20 @@
       <c r="R35" s="10"/>
       <c r="S35" s="10"/>
     </row>
-    <row r="36" spans="1:19" ht="21" x14ac:dyDescent="0.3">
-      <c r="B36" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E36"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C36" s="1">
+        <v>67</v>
+      </c>
+      <c r="D36" s="1">
+        <v>70</v>
+      </c>
+      <c r="E36" s="1">
+        <v>74</v>
+      </c>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
       <c r="N36" s="10"/>
       <c r="O36" s="10"/>
       <c r="P36" s="10"/>
@@ -1618,21 +1937,16 @@
       <c r="S36" s="10"/>
     </row>
     <row r="37" spans="1:19" ht="21" x14ac:dyDescent="0.3">
-      <c r="B37" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
+      <c r="B37" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
@@ -1644,24 +1958,42 @@
       <c r="R37" s="10"/>
       <c r="S37" s="10"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-    </row>
-    <row r="40" spans="1:19" ht="30" x14ac:dyDescent="0.45">
-      <c r="B40" s="5"/>
-      <c r="K40" s="6"/>
-      <c r="L40"/>
-      <c r="M40"/>
-      <c r="N40"/>
-      <c r="O40"/>
-      <c r="P40"/>
-    </row>
-    <row r="41" spans="1:19" ht="27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="B38" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+    </row>
+    <row r="41" spans="1:19" ht="30" x14ac:dyDescent="0.45">
       <c r="B41" s="5"/>
-      <c r="K41" s="7"/>
+      <c r="K41" s="6"/>
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41"/>
@@ -1670,17 +2002,12 @@
     </row>
     <row r="42" spans="1:19" ht="27" x14ac:dyDescent="0.3">
       <c r="B42" s="5"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
+      <c r="K42" s="7"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
     </row>
     <row r="43" spans="1:19" ht="27" x14ac:dyDescent="0.3">
       <c r="B43" s="5"/>
@@ -1690,14 +2017,19 @@
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="K43" s="8"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
     </row>
     <row r="44" spans="1:19" ht="27" x14ac:dyDescent="0.3">
       <c r="B44" s="5"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
       <c r="K44" s="8"/>
       <c r="L44" s="9"/>
       <c r="M44" s="9"/>
@@ -1705,7 +2037,8 @@
       <c r="O44" s="9"/>
       <c r="P44" s="9"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="27" x14ac:dyDescent="0.3">
+      <c r="B45" s="5"/>
       <c r="K45" s="8"/>
       <c r="L45" s="9"/>
       <c r="M45" s="9"/>
@@ -1713,6 +2046,14 @@
       <c r="O45" s="9"/>
       <c r="P45" s="9"/>
     </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K46" s="8"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/data/gravel/Panorama Katahdin 2.1 2025.xlsx
+++ b/data/gravel/Panorama Katahdin 2.1 2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EB58BC-8B50-B240-9750-012CC9DF011E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A0BE39-DF88-2647-9ABE-6247D501ACBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="23100" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -353,6 +353,24 @@
   </si>
   <si>
     <t>direct inquiry</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -691,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1120,68 +1138,68 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B39" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
         <v>67</v>
@@ -1189,108 +1207,108 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B47" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>81</v>
-      </c>
-      <c r="B50" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B57" t="s">
         <v>60</v>
@@ -1298,88 +1316,112 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>94</v>
+      </c>
+      <c r="B62" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="B64" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>102</v>
-      </c>
-      <c r="B65" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>105</v>
-      </c>
-      <c r="B67" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>107</v>
+        <v>102</v>
+      </c>
+      <c r="B68" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>103</v>
+      </c>
+      <c r="B69" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>108</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B72" t="s">
         <v>109</v>
       </c>
     </row>

--- a/data/gravel/Panorama Katahdin 2.1 2025.xlsx
+++ b/data/gravel/Panorama Katahdin 2.1 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A0BE39-DF88-2647-9ABE-6247D501ACBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4BB908-AA8F-0C4E-80DB-04A85BD6CC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="23100" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,9 +349,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>direct inquiry</t>
   </si>
   <si>
@@ -371,6 +368,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1042,7 @@
         <v>405</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1138,26 +1138,26 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
         <v>111</v>
-      </c>
-      <c r="B35" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" t="s">
         <v>113</v>
-      </c>
-      <c r="B36" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" t="s">
         <v>115</v>
-      </c>
-      <c r="B37" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1421,8 +1421,8 @@
       <c r="A72" t="s">
         <v>108</v>
       </c>
-      <c r="B72" t="s">
-        <v>109</v>
+      <c r="B72" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Panorama Katahdin 2.1 2025.xlsx
+++ b/data/gravel/Panorama Katahdin 2.1 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4BB908-AA8F-0C4E-80DB-04A85BD6CC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD83C0AF-4F0C-034A-868A-6AF68BB35823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23100" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5380" yWindow="500" windowWidth="23100" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -1201,32 +1201,20 @@
       <c r="A43" t="s">
         <v>66</v>
       </c>
-      <c r="B43" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>68</v>
       </c>
-      <c r="B44" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>69</v>
       </c>
-      <c r="B45" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>70</v>
-      </c>
-      <c r="B46" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Panorama Katahdin 2.1 2025.xlsx
+++ b/data/gravel/Panorama Katahdin 2.1 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD83C0AF-4F0C-034A-868A-6AF68BB35823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747E3D60-6EC2-C246-BA99-335EBF713C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5380" yWindow="500" windowWidth="23100" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://www.panoramacycles.com/cdn/shop/files/Katahdin25b-2.jpg?v=1748532182</t>
   </si>
 </sst>
 </file>
@@ -755,6 +758,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+    </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Panorama Katahdin 2.1 2025.xlsx
+++ b/data/gravel/Panorama Katahdin 2.1 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747E3D60-6EC2-C246-BA99-335EBF713C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0D91CE-4C03-F644-8332-3AA927331754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5380" yWindow="500" windowWidth="23100" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -374,6 +374,12 @@
   </si>
   <si>
     <t>https://www.panoramacycles.com/cdn/shop/files/Katahdin25b-2.jpg?v=1748532182</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Granby, Québec, Canada</t>
   </si>
 </sst>
 </file>
@@ -712,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1421,6 +1427,14 @@
         <v>116</v>
       </c>
     </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>118</v>
+      </c>
+      <c r="B73" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Panorama Katahdin 2.1 2025.xlsx
+++ b/data/gravel/Panorama Katahdin 2.1 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0D91CE-4C03-F644-8332-3AA927331754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA394E5A-2AC0-254E-95F0-0CB3BF4E5A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5380" yWindow="500" windowWidth="23100" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -380,6 +380,24 @@
   </si>
   <si>
     <t>Granby, Québec, Canada</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -718,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1249,137 +1267,122 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>75</v>
-      </c>
-      <c r="B49" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>78</v>
-      </c>
-      <c r="B51" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>80</v>
-      </c>
-      <c r="B52" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>81</v>
-      </c>
-      <c r="B53" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>83</v>
-      </c>
-      <c r="B54" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>87</v>
-      </c>
-      <c r="B56" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B58" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B63" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B64" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>91</v>
+      </c>
+      <c r="B65" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B66" t="s">
         <v>60</v>
@@ -1387,51 +1390,96 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>101</v>
+        <v>93</v>
+      </c>
+      <c r="B67" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B68" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B69" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>108</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
+      </c>
+      <c r="B72" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>102</v>
+      </c>
+      <c r="B74" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>103</v>
+      </c>
+      <c r="B75" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>105</v>
+      </c>
+      <c r="B76" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>108</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>118</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>119</v>
       </c>
     </row>
